--- a/website/public/templates/invoices-template.xlsx
+++ b/website/public/templates/invoices-template.xlsx
@@ -400,7 +400,7 @@
   <dimension ref="A1:Y4"/>
   <cols>
     <col min="1" max="1" width="21.83203125" customWidth="1"/>
-    <col min="2" max="2" width="22.83203125" customWidth="1"/>
+    <col min="2" max="2" width="18.83203125" customWidth="1"/>
     <col min="3" max="3" width="14.83203125" customWidth="1"/>
     <col min="4" max="4" width="24.83203125" customWidth="1"/>
     <col min="5" max="5" width="16.83203125" customWidth="1"/>
@@ -431,7 +431,7 @@
         <v>direction</v>
       </c>
       <c r="B1" t="str">
-        <v>partner_company_name</v>
+        <v>partner_name</v>
       </c>
       <c r="C1" t="str">
         <v>invoice_date</v>
@@ -508,7 +508,7 @@
         <v>Invoice direction</v>
       </c>
       <c r="B2" t="str">
-        <v>Partner company name</v>
+        <v>Partner name</v>
       </c>
       <c r="C2" t="str">
         <v>Invoice date</v>

--- a/website/public/templates/invoices-template.xlsx
+++ b/website/public/templates/invoices-template.xlsx
@@ -719,7 +719,7 @@
         <v>Required</v>
       </c>
       <c r="U4" t="str">
-        <v>Required for payable. Values: materials, labor, subcontractor, equipment_rental, permits_regulatory, other, software_licenses, partner_compensation, professional_services, other_sga</v>
+        <v>Required for payable. Values: materials, labor, subcontractor, equipment_rental, housing_food, other, software_licenses, partner_compensation, professional_services, other_sga</v>
       </c>
       <c r="V4" t="str">
         <v>Required, number</v>

--- a/website/public/templates/invoices-template.xlsx
+++ b/website/public/templates/invoices-template.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D39"/>
+  <dimension ref="A1:D38"/>
   <cols>
     <col min="1" max="1" width="28.83203125" customWidth="1"/>
     <col min="2" max="2" width="44.83203125" customWidth="1"/>
@@ -676,41 +676,41 @@
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>payment_method</v>
+        <v>quote_document_ref</v>
       </c>
       <c r="B25" t="str">
         <v>No</v>
       </c>
       <c r="C25" t="str">
-        <v>Payment method</v>
+        <v>Linked quote document_ref</v>
       </c>
       <c r="D25" t="str">
-        <v/>
+        <v>Must exist in DB</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>quote_document_ref</v>
+        <v>notes</v>
       </c>
       <c r="B26" t="str">
         <v>No</v>
       </c>
       <c r="C26" t="str">
-        <v>Linked quote document_ref</v>
+        <v>Notes</v>
       </c>
       <c r="D26" t="str">
-        <v>Must exist in DB</v>
+        <v/>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>notes</v>
+        <v>item_title</v>
       </c>
       <c r="B27" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="C27" t="str">
-        <v>Notes</v>
+        <v>Line item title</v>
       </c>
       <c r="D27" t="str">
         <v/>
@@ -718,123 +718,109 @@
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>item_title</v>
+        <v>category</v>
       </c>
       <c r="B28" t="str">
-        <v>Yes</v>
+        <v>Yes, for payable</v>
       </c>
       <c r="C28" t="str">
-        <v>Line item title</v>
+        <v>Line item category</v>
       </c>
       <c r="D28" t="str">
-        <v/>
+        <v>materials, labor, subcontractor, equipment_rental, housing_food, other, software_licenses, partner_compensation, professional_services, other_sga</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>category</v>
+        <v>subtotal</v>
       </c>
       <c r="B29" t="str">
-        <v>Yes, for payable</v>
+        <v>Yes</v>
       </c>
       <c r="C29" t="str">
-        <v>Line item category</v>
+        <v>Line item subtotal (before IGV)</v>
       </c>
       <c r="D29" t="str">
-        <v>materials, labor, subcontractor, equipment_rental, housing_food, other, software_licenses, partner_compensation, professional_services, other_sga</v>
+        <v>Number, &gt; 0</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>subtotal</v>
+        <v>quantity</v>
       </c>
       <c r="B30" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="C30" t="str">
-        <v>Line item subtotal (before IGV)</v>
+        <v>Line item quantity</v>
       </c>
       <c r="D30" t="str">
-        <v>Number, &gt; 0</v>
+        <v>Number</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>quantity</v>
+        <v>unit_of_measure</v>
       </c>
       <c r="B31" t="str">
         <v>No</v>
       </c>
       <c r="C31" t="str">
-        <v>Line item quantity</v>
+        <v>Unit of measure</v>
       </c>
       <c r="D31" t="str">
-        <v>Number</v>
+        <v/>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>unit_of_measure</v>
+        <v>unit_price</v>
       </c>
       <c r="B32" t="str">
         <v>No</v>
       </c>
       <c r="C32" t="str">
-        <v>Unit of measure</v>
+        <v>Unit price</v>
       </c>
       <c r="D32" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="str">
-        <v>unit_price</v>
-      </c>
-      <c r="B33" t="str">
-        <v>No</v>
-      </c>
-      <c r="C33" t="str">
-        <v>Unit price</v>
-      </c>
-      <c r="D33" t="str">
         <v>Number</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="str">
+        <v>Notes:</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>Notes:</v>
+        <v xml:space="preserve">  - Rows with the same document_ref are grouped into one invoice with multiple line items</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v xml:space="preserve">  - Rows with the same document_ref are grouped into one invoice with multiple line items</v>
+        <v xml:space="preserve">  - partner_name must match an entity tagged as "partner" in the database</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v xml:space="preserve">  - partner_name must match an entity tagged as "partner" in the database</v>
+        <v xml:space="preserve">  - Detracción only applies to PEN invoices</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v xml:space="preserve">  - Detracción only applies to PEN invoices</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="str">
         <v xml:space="preserve">  - Retención only applies to receivable invoices</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D39"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D38"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Y4"/>
+  <dimension ref="A1:X4"/>
   <cols>
     <col min="1" max="1" width="21.83203125" customWidth="1"/>
     <col min="2" max="2" width="18.83203125" customWidth="1"/>
@@ -852,15 +838,14 @@
     <col min="14" max="14" width="19.83203125" customWidth="1"/>
     <col min="15" max="15" width="29.83203125" customWidth="1"/>
     <col min="16" max="16" width="16.83203125" customWidth="1"/>
-    <col min="17" max="17" width="16.83203125" customWidth="1"/>
-    <col min="18" max="18" width="27.83203125" customWidth="1"/>
-    <col min="19" max="19" width="12.83203125" customWidth="1"/>
-    <col min="20" max="20" width="17.83203125" customWidth="1"/>
-    <col min="21" max="21" width="40.83203125" customWidth="1"/>
-    <col min="22" max="22" width="33.83203125" customWidth="1"/>
-    <col min="23" max="23" width="20.83203125" customWidth="1"/>
-    <col min="24" max="24" width="17.83203125" customWidth="1"/>
-    <col min="25" max="25" width="12.83203125" customWidth="1"/>
+    <col min="17" max="17" width="27.83203125" customWidth="1"/>
+    <col min="18" max="18" width="12.83203125" customWidth="1"/>
+    <col min="19" max="19" width="17.83203125" customWidth="1"/>
+    <col min="20" max="20" width="40.83203125" customWidth="1"/>
+    <col min="21" max="21" width="33.83203125" customWidth="1"/>
+    <col min="22" max="22" width="20.83203125" customWidth="1"/>
+    <col min="23" max="23" width="17.83203125" customWidth="1"/>
+    <col min="24" max="24" width="12.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -913,30 +898,27 @@
         <v>retencion_rate</v>
       </c>
       <c r="Q1" t="str">
-        <v>payment_method</v>
+        <v>quote_document_ref</v>
       </c>
       <c r="R1" t="str">
-        <v>quote_document_ref</v>
+        <v>notes</v>
       </c>
       <c r="S1" t="str">
-        <v>notes</v>
+        <v>item_title</v>
       </c>
       <c r="T1" t="str">
-        <v>item_title</v>
+        <v>category</v>
       </c>
       <c r="U1" t="str">
-        <v>category</v>
+        <v>subtotal</v>
       </c>
       <c r="V1" t="str">
-        <v>subtotal</v>
+        <v>quantity</v>
       </c>
       <c r="W1" t="str">
-        <v>quantity</v>
+        <v>unit_of_measure</v>
       </c>
       <c r="X1" t="str">
-        <v>unit_of_measure</v>
-      </c>
-      <c r="Y1" t="str">
         <v>unit_price</v>
       </c>
     </row>
@@ -990,30 +972,27 @@
         <v>Retención rate</v>
       </c>
       <c r="Q2" t="str">
-        <v>Payment method</v>
+        <v>Linked quote document_ref</v>
       </c>
       <c r="R2" t="str">
-        <v>Linked quote document_ref</v>
+        <v>Notes</v>
       </c>
       <c r="S2" t="str">
-        <v>Notes</v>
+        <v>Line item title</v>
       </c>
       <c r="T2" t="str">
-        <v>Line item title</v>
+        <v>Line item category</v>
       </c>
       <c r="U2" t="str">
-        <v>Line item category</v>
+        <v>Line item subtotal (before IGV)</v>
       </c>
       <c r="V2" t="str">
-        <v>Line item subtotal (before IGV)</v>
+        <v>Line item quantity</v>
       </c>
       <c r="W2" t="str">
-        <v>Line item quantity</v>
+        <v>Unit of measure</v>
       </c>
       <c r="X2" t="str">
-        <v>Unit of measure</v>
-      </c>
-      <c r="Y2" t="str">
         <v>Unit price</v>
       </c>
     </row>
@@ -1067,30 +1046,27 @@
         <v>0.03</v>
       </c>
       <c r="Q3" t="str">
-        <v>transfer</v>
+        <v>COT-001</v>
       </c>
       <c r="R3" t="str">
-        <v>COT-001</v>
+        <v/>
       </c>
       <c r="S3" t="str">
-        <v/>
+        <v>Cement bags</v>
       </c>
       <c r="T3" t="str">
-        <v>Cement bags</v>
+        <v>materials</v>
       </c>
       <c r="U3" t="str">
-        <v>materials</v>
+        <v>5000.00</v>
       </c>
       <c r="V3" t="str">
-        <v>5000.00</v>
+        <v>200</v>
       </c>
       <c r="W3" t="str">
-        <v>200</v>
+        <v>bags</v>
       </c>
       <c r="X3" t="str">
-        <v>bags</v>
-      </c>
-      <c r="Y3" t="str">
         <v>25.00</v>
       </c>
     </row>
@@ -1144,36 +1120,33 @@
         <v/>
       </c>
       <c r="Q4" t="str">
-        <v/>
+        <v>Must exist in DB</v>
       </c>
       <c r="R4" t="str">
-        <v>Must exist in DB</v>
+        <v/>
       </c>
       <c r="S4" t="str">
         <v/>
       </c>
       <c r="T4" t="str">
-        <v/>
+        <v>materials, labor, subcontractor, equipment_rental, housing_food, other, software_licenses, partner_compensation, professional_services, other_sga</v>
       </c>
       <c r="U4" t="str">
-        <v>materials, labor, subcontractor, equipment_rental, housing_food, other, software_licenses, partner_compensation, professional_services, other_sga</v>
+        <v>Number, &gt; 0</v>
       </c>
       <c r="V4" t="str">
-        <v>Number, &gt; 0</v>
+        <v>Number</v>
       </c>
       <c r="W4" t="str">
-        <v>Number</v>
+        <v/>
       </c>
       <c r="X4" t="str">
-        <v/>
-      </c>
-      <c r="Y4" t="str">
         <v>Number</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:Y4"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:X4"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/website/public/templates/invoices-template.xlsx
+++ b/website/public/templates/invoices-template.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D38"/>
+  <dimension ref="A1:D37"/>
   <cols>
     <col min="1" max="1" width="28.83203125" customWidth="1"/>
     <col min="2" max="2" width="44.83203125" customWidth="1"/>
@@ -676,27 +676,27 @@
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>quote_document_ref</v>
+        <v>notes</v>
       </c>
       <c r="B25" t="str">
         <v>No</v>
       </c>
       <c r="C25" t="str">
-        <v>Linked quote document_ref</v>
+        <v>Notes</v>
       </c>
       <c r="D25" t="str">
-        <v>Must exist in DB</v>
+        <v/>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>notes</v>
+        <v>item_title</v>
       </c>
       <c r="B26" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="C26" t="str">
-        <v>Notes</v>
+        <v>Line item title</v>
       </c>
       <c r="D26" t="str">
         <v/>
@@ -704,123 +704,109 @@
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>item_title</v>
+        <v>category</v>
       </c>
       <c r="B27" t="str">
-        <v>Yes</v>
+        <v>Yes, for payable</v>
       </c>
       <c r="C27" t="str">
-        <v>Line item title</v>
+        <v>Line item category</v>
       </c>
       <c r="D27" t="str">
-        <v/>
+        <v>materials, labor, subcontractor, equipment_rental, housing_food, other, software_licenses, partner_compensation, professional_services, other_sga</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>category</v>
+        <v>subtotal</v>
       </c>
       <c r="B28" t="str">
-        <v>Yes, for payable</v>
+        <v>Yes</v>
       </c>
       <c r="C28" t="str">
-        <v>Line item category</v>
+        <v>Line item subtotal (before IGV)</v>
       </c>
       <c r="D28" t="str">
-        <v>materials, labor, subcontractor, equipment_rental, housing_food, other, software_licenses, partner_compensation, professional_services, other_sga</v>
+        <v>Number, &gt; 0</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>subtotal</v>
+        <v>quantity</v>
       </c>
       <c r="B29" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="C29" t="str">
-        <v>Line item subtotal (before IGV)</v>
+        <v>Line item quantity</v>
       </c>
       <c r="D29" t="str">
-        <v>Number, &gt; 0</v>
+        <v>Number</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>quantity</v>
+        <v>unit_of_measure</v>
       </c>
       <c r="B30" t="str">
         <v>No</v>
       </c>
       <c r="C30" t="str">
-        <v>Line item quantity</v>
+        <v>Unit of measure</v>
       </c>
       <c r="D30" t="str">
-        <v>Number</v>
+        <v/>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>unit_of_measure</v>
+        <v>unit_price</v>
       </c>
       <c r="B31" t="str">
         <v>No</v>
       </c>
       <c r="C31" t="str">
-        <v>Unit of measure</v>
+        <v>Unit price</v>
       </c>
       <c r="D31" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="str">
-        <v>unit_price</v>
-      </c>
-      <c r="B32" t="str">
-        <v>No</v>
-      </c>
-      <c r="C32" t="str">
-        <v>Unit price</v>
-      </c>
-      <c r="D32" t="str">
         <v>Number</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="str">
+        <v>Notes:</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>Notes:</v>
+        <v xml:space="preserve">  - Rows with the same document_ref are grouped into one invoice with multiple line items</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v xml:space="preserve">  - Rows with the same document_ref are grouped into one invoice with multiple line items</v>
+        <v xml:space="preserve">  - partner_name must match an entity tagged as "partner" in the database</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v xml:space="preserve">  - partner_name must match an entity tagged as "partner" in the database</v>
+        <v xml:space="preserve">  - Detracción only applies to PEN invoices</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v xml:space="preserve">  - Detracción only applies to PEN invoices</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="str">
         <v xml:space="preserve">  - Retención only applies to receivable invoices</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D38"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D37"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:X4"/>
+  <dimension ref="A1:W4"/>
   <cols>
     <col min="1" max="1" width="21.83203125" customWidth="1"/>
     <col min="2" max="2" width="18.83203125" customWidth="1"/>
@@ -838,14 +824,13 @@
     <col min="14" max="14" width="19.83203125" customWidth="1"/>
     <col min="15" max="15" width="29.83203125" customWidth="1"/>
     <col min="16" max="16" width="16.83203125" customWidth="1"/>
-    <col min="17" max="17" width="27.83203125" customWidth="1"/>
-    <col min="18" max="18" width="12.83203125" customWidth="1"/>
-    <col min="19" max="19" width="17.83203125" customWidth="1"/>
-    <col min="20" max="20" width="40.83203125" customWidth="1"/>
-    <col min="21" max="21" width="33.83203125" customWidth="1"/>
-    <col min="22" max="22" width="20.83203125" customWidth="1"/>
-    <col min="23" max="23" width="17.83203125" customWidth="1"/>
-    <col min="24" max="24" width="12.83203125" customWidth="1"/>
+    <col min="17" max="17" width="12.83203125" customWidth="1"/>
+    <col min="18" max="18" width="17.83203125" customWidth="1"/>
+    <col min="19" max="19" width="40.83203125" customWidth="1"/>
+    <col min="20" max="20" width="33.83203125" customWidth="1"/>
+    <col min="21" max="21" width="20.83203125" customWidth="1"/>
+    <col min="22" max="22" width="17.83203125" customWidth="1"/>
+    <col min="23" max="23" width="12.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -898,27 +883,24 @@
         <v>retencion_rate</v>
       </c>
       <c r="Q1" t="str">
-        <v>quote_document_ref</v>
+        <v>notes</v>
       </c>
       <c r="R1" t="str">
-        <v>notes</v>
+        <v>item_title</v>
       </c>
       <c r="S1" t="str">
-        <v>item_title</v>
+        <v>category</v>
       </c>
       <c r="T1" t="str">
-        <v>category</v>
+        <v>subtotal</v>
       </c>
       <c r="U1" t="str">
-        <v>subtotal</v>
+        <v>quantity</v>
       </c>
       <c r="V1" t="str">
-        <v>quantity</v>
+        <v>unit_of_measure</v>
       </c>
       <c r="W1" t="str">
-        <v>unit_of_measure</v>
-      </c>
-      <c r="X1" t="str">
         <v>unit_price</v>
       </c>
     </row>
@@ -972,27 +954,24 @@
         <v>Retención rate</v>
       </c>
       <c r="Q2" t="str">
-        <v>Linked quote document_ref</v>
+        <v>Notes</v>
       </c>
       <c r="R2" t="str">
-        <v>Notes</v>
+        <v>Line item title</v>
       </c>
       <c r="S2" t="str">
-        <v>Line item title</v>
+        <v>Line item category</v>
       </c>
       <c r="T2" t="str">
-        <v>Line item category</v>
+        <v>Line item subtotal (before IGV)</v>
       </c>
       <c r="U2" t="str">
-        <v>Line item subtotal (before IGV)</v>
+        <v>Line item quantity</v>
       </c>
       <c r="V2" t="str">
-        <v>Line item quantity</v>
+        <v>Unit of measure</v>
       </c>
       <c r="W2" t="str">
-        <v>Unit of measure</v>
-      </c>
-      <c r="X2" t="str">
         <v>Unit price</v>
       </c>
     </row>
@@ -1046,27 +1025,24 @@
         <v>0.03</v>
       </c>
       <c r="Q3" t="str">
-        <v>COT-001</v>
+        <v/>
       </c>
       <c r="R3" t="str">
-        <v/>
+        <v>Cement bags</v>
       </c>
       <c r="S3" t="str">
-        <v>Cement bags</v>
+        <v>materials</v>
       </c>
       <c r="T3" t="str">
-        <v>materials</v>
+        <v>5000.00</v>
       </c>
       <c r="U3" t="str">
-        <v>5000.00</v>
+        <v>200</v>
       </c>
       <c r="V3" t="str">
-        <v>200</v>
+        <v>bags</v>
       </c>
       <c r="W3" t="str">
-        <v>bags</v>
-      </c>
-      <c r="X3" t="str">
         <v>25.00</v>
       </c>
     </row>
@@ -1120,33 +1096,30 @@
         <v/>
       </c>
       <c r="Q4" t="str">
-        <v>Must exist in DB</v>
+        <v/>
       </c>
       <c r="R4" t="str">
         <v/>
       </c>
       <c r="S4" t="str">
-        <v/>
+        <v>materials, labor, subcontractor, equipment_rental, housing_food, other, software_licenses, partner_compensation, professional_services, other_sga</v>
       </c>
       <c r="T4" t="str">
-        <v>materials, labor, subcontractor, equipment_rental, housing_food, other, software_licenses, partner_compensation, professional_services, other_sga</v>
+        <v>Number, &gt; 0</v>
       </c>
       <c r="U4" t="str">
-        <v>Number, &gt; 0</v>
+        <v>Number</v>
       </c>
       <c r="V4" t="str">
-        <v>Number</v>
+        <v/>
       </c>
       <c r="W4" t="str">
-        <v/>
-      </c>
-      <c r="X4" t="str">
         <v>Number</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:X4"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:W4"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/website/public/templates/invoices-template.xlsx
+++ b/website/public/templates/invoices-template.xlsx
@@ -542,10 +542,10 @@
         <v>Yes</v>
       </c>
       <c r="C15" t="str">
-        <v>IGV rate</v>
+        <v>IGV rate (%)</v>
       </c>
       <c r="D15" t="str">
-        <v>0 or 0.18</v>
+        <v>0 or 18</v>
       </c>
     </row>
     <row r="16">
@@ -601,7 +601,7 @@
         <v>Comprobante type</v>
       </c>
       <c r="D19" t="str">
-        <v>factura, boleta, recibo_por_honorarios, liquidacion_de_compra, planilla_jornales, none</v>
+        <v>factura, boleta, recibo_por_honorarios, liquidacion_de_compra, planilla_jornales, none, pending</v>
       </c>
     </row>
     <row r="20">
@@ -640,10 +640,10 @@
         <v>No</v>
       </c>
       <c r="C22" t="str">
-        <v>Detracción rate</v>
+        <v>Detracción rate (%)</v>
       </c>
       <c r="D22" t="str">
-        <v>PEN invoices only</v>
+        <v>0–100, PEN invoices only</v>
       </c>
     </row>
     <row r="23">
@@ -668,10 +668,10 @@
         <v>No</v>
       </c>
       <c r="C24" t="str">
-        <v>Retención rate</v>
+        <v>Retención rate (%)</v>
       </c>
       <c r="D24" t="str">
-        <v/>
+        <v>0–100, receivable only</v>
       </c>
     </row>
     <row r="25">
@@ -814,16 +814,16 @@
     <col min="4" max="4" width="24.83203125" customWidth="1"/>
     <col min="5" max="5" width="16.83203125" customWidth="1"/>
     <col min="6" max="6" width="15.83203125" customWidth="1"/>
-    <col min="7" max="7" width="12.83203125" customWidth="1"/>
+    <col min="7" max="7" width="14.83203125" customWidth="1"/>
     <col min="8" max="8" width="29.83203125" customWidth="1"/>
     <col min="9" max="9" width="18.83203125" customWidth="1"/>
     <col min="10" max="10" width="24.83203125" customWidth="1"/>
     <col min="11" max="11" width="40.83203125" customWidth="1"/>
     <col min="12" max="12" width="35.83203125" customWidth="1"/>
     <col min="13" max="13" width="12.83203125" customWidth="1"/>
-    <col min="14" max="14" width="19.83203125" customWidth="1"/>
+    <col min="14" max="14" width="26.83203125" customWidth="1"/>
     <col min="15" max="15" width="29.83203125" customWidth="1"/>
-    <col min="16" max="16" width="16.83203125" customWidth="1"/>
+    <col min="16" max="16" width="24.83203125" customWidth="1"/>
     <col min="17" max="17" width="12.83203125" customWidth="1"/>
     <col min="18" max="18" width="17.83203125" customWidth="1"/>
     <col min="19" max="19" width="40.83203125" customWidth="1"/>
@@ -924,7 +924,7 @@
         <v>Currency code</v>
       </c>
       <c r="G2" t="str">
-        <v>IGV rate</v>
+        <v>IGV rate (%)</v>
       </c>
       <c r="H2" t="str">
         <v>Exchange rate (PEN per USD)</v>
@@ -945,13 +945,13 @@
         <v>Due date</v>
       </c>
       <c r="N2" t="str">
-        <v>Detracción rate</v>
+        <v>Detracción rate (%)</v>
       </c>
       <c r="O2" t="str">
         <v>Retención applies?</v>
       </c>
       <c r="P2" t="str">
-        <v>Retención rate</v>
+        <v>Retención rate (%)</v>
       </c>
       <c r="Q2" t="str">
         <v>Notes</v>
@@ -995,7 +995,7 @@
         <v>PEN</v>
       </c>
       <c r="G3" t="str">
-        <v>0.18</v>
+        <v>18</v>
       </c>
       <c r="H3" t="str">
         <v>3.72</v>
@@ -1016,13 +1016,13 @@
         <v>2026-04-15</v>
       </c>
       <c r="N3" t="str">
-        <v>0.12</v>
+        <v>12</v>
       </c>
       <c r="O3" t="str">
         <v>false</v>
       </c>
       <c r="P3" t="str">
-        <v>0.03</v>
+        <v>3</v>
       </c>
       <c r="Q3" t="str">
         <v/>
@@ -1066,7 +1066,7 @@
         <v>USD, PEN</v>
       </c>
       <c r="G4" t="str">
-        <v>0 or 0.18</v>
+        <v>0 or 18</v>
       </c>
       <c r="H4" t="str">
         <v>2.5–6.0</v>
@@ -1078,7 +1078,7 @@
         <v>Must exist in DB</v>
       </c>
       <c r="K4" t="str">
-        <v>factura, boleta, recibo_por_honorarios, liquidacion_de_compra, planilla_jornales, none</v>
+        <v>factura, boleta, recibo_por_honorarios, liquidacion_de_compra, planilla_jornales, none, pending</v>
       </c>
       <c r="L4" t="str">
         <v/>
@@ -1087,13 +1087,13 @@
         <v>YYYY-MM-DD</v>
       </c>
       <c r="N4" t="str">
-        <v>PEN invoices only</v>
+        <v>0–100, PEN invoices only</v>
       </c>
       <c r="O4" t="str">
         <v>true/false, receivable only</v>
       </c>
       <c r="P4" t="str">
-        <v/>
+        <v>0–100, receivable only</v>
       </c>
       <c r="Q4" t="str">
         <v/>

--- a/website/public/templates/invoices-template.xlsx
+++ b/website/public/templates/invoices-template.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D37"/>
+  <dimension ref="A1:D38"/>
   <cols>
     <col min="1" max="1" width="28.83203125" customWidth="1"/>
     <col min="2" max="2" width="44.83203125" customWidth="1"/>
@@ -668,7 +668,7 @@
         <v>No</v>
       </c>
       <c r="C24" t="str">
-        <v>Retención rate (%)</v>
+        <v>Retención rate (%). Defaults to 8% if retencion_applicable=true</v>
       </c>
       <c r="D24" t="str">
         <v>0–100, receivable only</v>
@@ -797,9 +797,14 @@
         <v xml:space="preserve">  - Retención only applies to receivable invoices</v>
       </c>
     </row>
+    <row r="38">
+      <c r="A38" t="str">
+        <v xml:space="preserve">  - If retencion_applicable=true and no retencion_rate is provided, defaults to 8%</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D37"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D38"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -823,7 +828,7 @@
     <col min="13" max="13" width="12.83203125" customWidth="1"/>
     <col min="14" max="14" width="26.83203125" customWidth="1"/>
     <col min="15" max="15" width="29.83203125" customWidth="1"/>
-    <col min="16" max="16" width="24.83203125" customWidth="1"/>
+    <col min="16" max="16" width="40.83203125" customWidth="1"/>
     <col min="17" max="17" width="12.83203125" customWidth="1"/>
     <col min="18" max="18" width="17.83203125" customWidth="1"/>
     <col min="19" max="19" width="40.83203125" customWidth="1"/>
@@ -951,7 +956,7 @@
         <v>Retención applies?</v>
       </c>
       <c r="P2" t="str">
-        <v>Retención rate (%)</v>
+        <v>Retención rate (%). Defaults to 8% if retencion_applicable=true</v>
       </c>
       <c r="Q2" t="str">
         <v>Notes</v>
@@ -1022,7 +1027,7 @@
         <v>false</v>
       </c>
       <c r="P3" t="str">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="Q3" t="str">
         <v/>

--- a/website/public/templates/invoices-template.xlsx
+++ b/website/public/templates/invoices-template.xlsx
@@ -556,7 +556,7 @@
         <v>Yes</v>
       </c>
       <c r="C16" t="str">
-        <v>Exchange rate (PEN per USD)</v>
+        <v>Exchange rate (PEN per USD). Auto-filled from DB if blank</v>
       </c>
       <c r="D16" t="str">
         <v>2.5–6.0</v>
@@ -820,7 +820,7 @@
     <col min="5" max="5" width="16.83203125" customWidth="1"/>
     <col min="6" max="6" width="15.83203125" customWidth="1"/>
     <col min="7" max="7" width="14.83203125" customWidth="1"/>
-    <col min="8" max="8" width="29.83203125" customWidth="1"/>
+    <col min="8" max="8" width="40.83203125" customWidth="1"/>
     <col min="9" max="9" width="18.83203125" customWidth="1"/>
     <col min="10" max="10" width="24.83203125" customWidth="1"/>
     <col min="11" max="11" width="40.83203125" customWidth="1"/>
@@ -932,7 +932,7 @@
         <v>IGV rate (%)</v>
       </c>
       <c r="H2" t="str">
-        <v>Exchange rate (PEN per USD)</v>
+        <v>Exchange rate (PEN per USD). Auto-filled from DB if blank</v>
       </c>
       <c r="I2" t="str">
         <v>Project code</v>
